--- a/web/files/港岛-北角-海璇 II (第2B-3期).xlsx
+++ b/web/files/港岛-北角-海璇 II (第2B-3期).xlsx
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 670呎 (3房)
+          <t>A | 671呎 (3房)
 -
 -
 (待售)</t>
@@ -18493,7 +18493,7 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>E | 387呎 (1房)
+          <t>E | 386呎 (1房)
 -
 -
 (待售)</t>

--- a/web/files/港岛-北角-海璇 II (第2B-3期).xlsx
+++ b/web/files/港岛-北角-海璇 II (第2B-3期).xlsx
@@ -9451,19 +9451,23 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="H130" s="5" t="n">
-        <v>68270000</v>
-      </c>
-      <c r="I130" s="5" t="n">
-        <v>134126</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -17441,7 +17445,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -17451,7 +17455,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -18087,12 +18091,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 509呎 (2房)
-$6827万
-$134,126/呎
-(25年-05月-20日)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">

--- a/web/files/港岛-北角-海璇 II (第2B-3期).xlsx
+++ b/web/files/港岛-北角-海璇 II (第2B-3期).xlsx
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2115</v>
+        <v>2118</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>136800000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>64681</v>
+        <v>64589</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>50129988</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>44879</v>
+        <v>43067</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1438</v>
+        <v>1484</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>70259980</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>48860</v>
+        <v>47345</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>46800000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>41898</v>
+        <v>40206</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1438</v>
+        <v>1484</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>64108800</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>44582</v>
+        <v>43200</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>46420000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>41558</v>
+        <v>39880</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1438</v>
+        <v>1484</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>62773200</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>43653</v>
+        <v>42300</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>45978000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>41162</v>
+        <v>39500</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1438</v>
+        <v>1484</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>61290000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>42622</v>
+        <v>41301</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45380000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>40627</v>
+        <v>38986</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1438</v>
+        <v>1484</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>67312000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>46809</v>
+        <v>45358</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>43968000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>39363</v>
+        <v>37773</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1438</v>
+        <v>1484</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>66372000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>46156</v>
+        <v>44725</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>44362100</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>39715</v>
+        <v>38112</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1438</v>
+        <v>1484</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>61586000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>42828</v>
+        <v>41500</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>45370429</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>40618</v>
+        <v>38978</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1438</v>
+        <v>1484</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>56095200</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>39009</v>
+        <v>37800</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>42200000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>37780</v>
+        <v>36254</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1438</v>
+        <v>1484</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>54380000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>37816</v>
+        <v>36644</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>39600000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>35452</v>
+        <v>34021</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1438</v>
+        <v>1484</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>56000000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>38943</v>
+        <v>37736</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>40158000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>35952</v>
+        <v>34500</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1438</v>
+        <v>1484</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>52682000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>36636</v>
+        <v>35500</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1063</v>
+        <v>1110</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>42180000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>39680</v>
+        <v>38000</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1372</v>
+        <v>1418</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>68064000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>49609</v>
+        <v>48000</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2058</v>
+        <v>2108</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>128634000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>62504</v>
+        <v>61022</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1107</v>
+        <v>1153</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>48500000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>43812</v>
+        <v>42064</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>63786000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>44388</v>
+        <v>43011</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1107</v>
+        <v>1153</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>47273000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>42704</v>
+        <v>41000</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>59023400</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>41074</v>
+        <v>39800</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1107</v>
+        <v>1153</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>46454370</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>41964</v>
+        <v>40290</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>60080000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>41809</v>
+        <v>40512</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1107</v>
+        <v>1153</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>44500000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>40199</v>
+        <v>38595</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>57388000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>39936</v>
+        <v>38697</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1107</v>
+        <v>1153</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>50005500</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>45172</v>
+        <v>43370</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>54500250</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>37926</v>
+        <v>36750</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1107</v>
+        <v>1153</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>42800000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>38663</v>
+        <v>37121</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>58868888</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>40967</v>
+        <v>39696</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1107</v>
+        <v>1153</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>41188000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>37207</v>
+        <v>35722</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>54543989</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>37957</v>
+        <v>36779</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1107</v>
+        <v>1153</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>42139888</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>38067</v>
+        <v>36548</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1107</v>
+        <v>1153</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>41000118</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>37037</v>
+        <v>35560</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>53721680</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>37385</v>
+        <v>36225</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1107</v>
+        <v>1153</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>40868100</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>36918</v>
+        <v>35445</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>54680000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>38051</v>
+        <v>36871</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1107</v>
+        <v>1153</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>39200000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>35411</v>
+        <v>33998</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>49680500</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>34572</v>
+        <v>33500</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>51163500</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>35604</v>
+        <v>34500</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1090</v>
+        <v>1137</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>42888888</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>39348</v>
+        <v>37721</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>54778860</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>38120</v>
+        <v>36938</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="E137" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="E179" s="4" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         </is>
       </c>
       <c r="E201" s="4" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         </is>
       </c>
       <c r="E219" s="4" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -16630,9 +16630,9 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 2115呎 (开放式)
+          <t>A | 2118呎 (开放式)
 $13680万
-$64,681/呎
+$64,589/呎
 (25年-11月-11日)</t>
         </is>
       </c>
@@ -16646,17 +16646,17 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>A | 1438呎 (4+房)
+          <t>A | 1484呎 (4+房)
 $7026万
-$48,860/呎
+$47,345/呎
 (25年-04月-23日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>B | 1117呎 (3房)
+          <t>B | 1164呎 (3房)
 $5013万
-$44,879/呎
+$43,067/呎
 (25年-04月-23日)</t>
         </is>
       </c>
@@ -16669,17 +16669,17 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 1438呎 (4+房)
+          <t>A | 1484呎 (4+房)
 $6411万
-$44,582/呎
+$43,200/呎
 (25年-04月-23日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>B | 1117呎 (3房)
+          <t>B | 1164呎 (3房)
 $4680万
-$41,898/呎
+$40,206/呎
 (25年-04月-03日)</t>
         </is>
       </c>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>A | 1438呎 (4+房)
+          <t>A | 1484呎 (4+房)
 $6277万
-$43,653/呎
+$42,300/呎
 (25年-03月-27日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>B | 1117呎 (3房)
+          <t>B | 1164呎 (3房)
 $4642万
-$41,558/呎
+$39,880/呎
 (25年-04月-30日)</t>
         </is>
       </c>
@@ -16715,17 +16715,17 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 1438呎 (4+房)
+          <t>A | 1484呎 (4+房)
 $6129万
-$42,622/呎
+$41,301/呎
 (24年-12月-05日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>B | 1117呎 (3房)
+          <t>B | 1164呎 (3房)
 $4598万
-$41,162/呎
+$39,500/呎
 (25年-03月-19日)</t>
         </is>
       </c>
@@ -16738,17 +16738,17 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>A | 1438呎 (4+房)
+          <t>A | 1484呎 (4+房)
 $6731万
-$46,809/呎
+$45,358/呎
 (24年-12月-06日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>B | 1117呎 (3房)
+          <t>B | 1164呎 (3房)
 $4538万
-$40,627/呎
+$38,986/呎
 (24年-12月-19日)</t>
         </is>
       </c>
@@ -16761,17 +16761,17 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 1438呎 (4+房)
+          <t>A | 1484呎 (4+房)
 $6637万
-$46,156/呎
+$44,725/呎
 (24年-12月-19日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>B | 1117呎 (3房)
+          <t>B | 1164呎 (3房)
 $4397万
-$39,363/呎
+$37,773/呎
 (24年-12月-20日)</t>
         </is>
       </c>
@@ -16784,17 +16784,17 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>A | 1438呎 (4+房)
+          <t>A | 1484呎 (4+房)
 $6159万
-$42,828/呎
+$41,500/呎
 (25年-04月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 1117呎 (3房)
+          <t>B | 1164呎 (3房)
 $4436万
-$39,715/呎
+$38,112/呎
 (25年-05月-09日)</t>
         </is>
       </c>
@@ -16807,17 +16807,17 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 1438呎 (4+房)
+          <t>A | 1484呎 (4+房)
 $5610万
-$39,009/呎
+$37,800/呎
 (24年-11月-21日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>B | 1117呎 (3房)
+          <t>B | 1164呎 (3房)
 $4537万
-$40,618/呎
+$38,978/呎
 (24年-12月-30日)</t>
         </is>
       </c>
@@ -16830,17 +16830,17 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 1438呎 (4+房)
+          <t>A | 1484呎 (4+房)
 $5438万
-$37,816/呎
+$36,644/呎
 (25年-04月-10日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>B | 1117呎 (3房)
+          <t>B | 1164呎 (3房)
 $4220万
-$37,780/呎
+$36,254/呎
 (25年-04月-09日)</t>
         </is>
       </c>
@@ -16853,17 +16853,17 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>A | 1438呎 (4+房)
+          <t>A | 1484呎 (4+房)
 $5600万
-$38,943/呎
+$37,736/呎
 (24年-12月-11日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>B | 1117呎 (3房)
+          <t>B | 1164呎 (3房)
 $3960万
-$35,452/呎
+$34,021/呎
 (25年-03月-03日)</t>
         </is>
       </c>
@@ -16876,17 +16876,17 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>A | 1438呎 (4+房)
+          <t>A | 1484呎 (4+房)
 $5268万
-$36,636/呎
+$35,500/呎
 (25年-05月-15日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>B | 1117呎 (3房)
+          <t>B | 1164呎 (3房)
 $4016万
-$35,952/呎
+$34,500/呎
 (25年-03月-27日)</t>
         </is>
       </c>
@@ -16899,17 +16899,17 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>A | 1372呎 (4+房)
+          <t>A | 1418呎 (4+房)
 $6806万
-$49,609/呎
+$48,000/呎
 (25年-04月-10日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>B | 1063呎 (3房)
+          <t>B | 1110呎 (3房)
 $4218万
-$39,680/呎
+$38,000/呎
 (24年-12月-20日)</t>
         </is>
       </c>
@@ -17049,9 +17049,9 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 2058呎 (4+房)
+          <t>A | 2108呎 (4+房)
 $12863万
-$62,504/呎
+$61,022/呎
 (24年-11月-12日)</t>
         </is>
       </c>
@@ -17065,17 +17065,17 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $6379万
-$44,388/呎
+$43,011/呎
 (24年-11月-13日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>B | 1107呎 (3房)
+          <t>B | 1153呎 (3房)
 $4850万
-$43,812/呎
+$42,064/呎
 (25年-01月-13日)</t>
         </is>
       </c>
@@ -17088,17 +17088,17 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $5902万
-$41,074/呎
+$39,800/呎
 (24年-10月-31日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>B | 1107呎 (3房)
+          <t>B | 1153呎 (3房)
 $4727万
-$42,704/呎
+$41,000/呎
 (24年-11月-15日)</t>
         </is>
       </c>
@@ -17111,17 +17111,17 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $6008万
-$41,809/呎
+$40,512/呎
 (24年-11月-07日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>B | 1107呎 (3房)
+          <t>B | 1153呎 (3房)
 $4645万
-$41,964/呎
+$40,290/呎
 (24年-11月-07日)</t>
         </is>
       </c>
@@ -17134,17 +17134,17 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $5739万
-$39,936/呎
+$38,697/呎
 (24年-10月-17日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>B | 1107呎 (3房)
+          <t>B | 1153呎 (3房)
 $4450万
-$40,199/呎
+$38,595/呎
 (24年-10月-29日)</t>
         </is>
       </c>
@@ -17157,17 +17157,17 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $5450万
-$37,926/呎
+$36,750/呎
 (24年-10月-18日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>B | 1107呎 (3房)
+          <t>B | 1153呎 (3房)
 $5001万
-$45,172/呎
+$43,370/呎
 (24年-11月-11日)</t>
         </is>
       </c>
@@ -17180,17 +17180,17 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $5887万
-$40,967/呎
+$39,696/呎
 (24年-10月-28日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>B | 1107呎 (3房)
+          <t>B | 1153呎 (3房)
 $4280万
-$38,663/呎
+$37,121/呎
 (24年-10月-24日)</t>
         </is>
       </c>
@@ -17203,17 +17203,17 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $5454万
-$37,957/呎
+$36,779/呎
 (24年-10月-24日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 1107呎 (3房)
+          <t>B | 1153呎 (3房)
 $4119万
-$37,207/呎
+$35,722/呎
 (24年-10月-29日)</t>
         </is>
       </c>
@@ -17234,9 +17234,9 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>B | 1107呎 (3房)
+          <t>B | 1153呎 (3房)
 $4214万
-$38,067/呎
+$36,548/呎
 (24年-12月-02日)</t>
         </is>
       </c>
@@ -17249,17 +17249,17 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $5372万
-$37,385/呎
+$36,225/呎
 (24年-11月-08日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>B | 1107呎 (3房)
+          <t>B | 1153呎 (3房)
 $4100万
-$37,037/呎
+$35,560/呎
 (24年-11月-01日)</t>
         </is>
       </c>
@@ -17272,17 +17272,17 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $5468万
-$38,051/呎
+$36,871/呎
 (24年-10月-30日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>B | 1107呎 (3房)
+          <t>B | 1153呎 (3房)
 $4087万
-$36,918/呎
+$35,445/呎
 (24年-10月-30日)</t>
         </is>
       </c>
@@ -17295,17 +17295,17 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $4968万
-$34,572/呎
+$33,500/呎
 (24年-11月-01日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>B | 1107呎 (3房)
+          <t>B | 1153呎 (3房)
 $3920万
-$35,411/呎
+$33,998/呎
 (24年-10月-21日)</t>
         </is>
       </c>
@@ -17318,9 +17318,9 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $5116万
-$35,604/呎
+$34,500/呎
 (24年-11月-19日)</t>
         </is>
       </c>
@@ -17341,17 +17341,17 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $5478万
-$38,120/呎
+$36,938/呎
 (24年-11月-28日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>B | 1090呎 (3房)
+          <t>B | 1137呎 (3房)
 $4289万
-$39,348/呎
+$37,721/呎
 (24年-11月-19日)</t>
         </is>
       </c>
@@ -17529,7 +17529,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 959呎 (3房)
+          <t>A | 960呎 (3房)
 -
 -
 (待售)</t>
@@ -17554,7 +17554,7 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>E | 386呎 (1房)
+          <t>E | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>H | 358呎 (1房)
+          <t>H | 361呎 (1房)
 -
 -
 (待售)</t>
@@ -17602,7 +17602,7 @@
       </c>
       <c r="L5" s="20" t="inlineStr">
         <is>
-          <t>L | 372呎 (1房)
+          <t>L | 373呎 (1房)
 -
 -
 (待售)</t>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 1053呎 (3房)
+          <t>A | 1052呎 (3房)
 -
 -
 (待售)</t>
@@ -17650,7 +17650,7 @@
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>F | 386呎 (1房)
+          <t>F | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -17785,7 +17785,7 @@
       </c>
       <c r="L7" s="20" t="inlineStr">
         <is>
-          <t>L | 372呎 (1房)
+          <t>L | 373呎 (1房)
 -
 -
 (待售)</t>
@@ -17824,7 +17824,7 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>D | 353呎 (1房)
+          <t>D | 356呎 (1房)
 -
 -
 (待售)</t>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>F | 386呎 (1房)
+          <t>F | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="L9" s="20" t="inlineStr">
         <is>
-          <t>L | 372呎 (1房)
+          <t>L | 373呎 (1房)
 -
 -
 (待售)</t>
@@ -17998,7 +17998,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 509呎 (2房)
+          <t>B | 512呎 (2房)
 -
 -
 (待售)</t>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 671呎 (3房)
+          <t>A | 670呎 (3房)
 -
 -
 (待售)</t>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 509呎 (2房)
+          <t>B | 512呎 (2房)
 -
 -
 (待售)</t>
@@ -18141,7 +18141,7 @@
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>H | 358呎 (1房)
+          <t>H | 361呎 (1房)
 -
 -
 (待售)</t>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 671呎 (3房)
+          <t>A | 670呎 (3房)
 -
 -
 (待售)</t>
@@ -18188,7 +18188,7 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 509呎 (2房)
+          <t>B | 512呎 (2房)
 -
 -
 (待售)</t>
@@ -18204,7 +18204,7 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>D | 353呎 (1房)
+          <t>D | 356呎 (1房)
 -
 -
 (待售)</t>
@@ -18220,7 +18220,7 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>F | 386呎 (1房)
+          <t>F | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -18236,7 +18236,7 @@
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>H | 358呎 (1房)
+          <t>H | 361呎 (1房)
 -
 -
 (待售)</t>
@@ -18283,7 +18283,7 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 509呎 (2房)
+          <t>B | 512呎 (2房)
 -
 -
 (待售)</t>
@@ -18299,7 +18299,7 @@
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>D | 353呎 (1房)
+          <t>D | 356呎 (1房)
 -
 -
 (待售)</t>
@@ -18307,7 +18307,7 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>E | 386呎 (1房)
+          <t>E | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
-          <t>L | 372呎 (1房)
+          <t>L | 373呎 (1房)
 -
 -
 (待售)</t>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 671呎 (3房)
+          <t>A | 670呎 (3房)
 -
 -
 (待售)</t>
@@ -18378,7 +18378,7 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 509呎 (2房)
+          <t>B | 512呎 (2房)
 -
 -
 (待售)</t>
@@ -18410,7 +18410,7 @@
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>F | 386呎 (1房)
+          <t>F | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>H | 358呎 (1房)
+          <t>H | 361呎 (1房)
 -
 -
 (待售)</t>
@@ -18450,7 +18450,7 @@
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>L | 372呎 (1房)
+          <t>L | 373呎 (1房)
 -
 -
 (待售)</t>
@@ -18465,7 +18465,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 671呎 (3房)
+          <t>A | 670呎 (3房)
 -
 -
 (待售)</t>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 509呎 (2房)
+          <t>B | 512呎 (2房)
 -
 -
 (待售)</t>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>E | 386呎 (1房)
+          <t>E | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>F | 386呎 (1房)
+          <t>F | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 671呎 (3房)
+          <t>A | 670呎 (3房)
 -
 -
 (待售)</t>
@@ -18568,7 +18568,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 509呎 (2房)
+          <t>B | 512呎 (2房)
 -
 -
 (待售)</t>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>D | 353呎 (1房)
+          <t>D | 356呎 (1房)
 -
 -
 (待售)</t>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>E | 386呎 (1房)
+          <t>E | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>F | 386呎 (1房)
+          <t>F | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -18616,7 +18616,7 @@
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>H | 358呎 (1房)
+          <t>H | 361呎 (1房)
 -
 -
 (待售)</t>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 671呎 (3房)
+          <t>A | 670呎 (3房)
 -
 -
 (待售)</t>
@@ -18663,7 +18663,7 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 509呎 (2房)
+          <t>B | 512呎 (2房)
 -
 -
 (待售)</t>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>A | 671呎 (3房)
+          <t>A | 670呎 (3房)
 -
 -
 (待售)</t>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 509呎 (2房)
+          <t>B | 512呎 (2房)
 -
 -
 (待售)</t>
@@ -18790,7 +18790,7 @@
       </c>
       <c r="G18" s="20" t="inlineStr">
         <is>
-          <t>F | 386呎 (1房)
+          <t>F | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
-          <t>H | 358呎 (1房)
+          <t>H | 361呎 (1房)
 -
 -
 (待售)</t>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 671呎 (3房)
+          <t>A | 670呎 (3房)
 -
 -
 (待售)</t>
@@ -18853,7 +18853,7 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 509呎 (2房)
+          <t>B | 512呎 (2房)
 -
 -
 (待售)</t>
@@ -18885,7 +18885,7 @@
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>F | 386呎 (1房)
+          <t>F | 387呎 (1房)
 -
 -
 (待售)</t>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>H | 358呎 (1房)
+          <t>H | 361呎 (1房)
 -
 -
 (待售)</t>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 509呎 (2房)
+          <t>B | 512呎 (2房)
 -
 -
 (待售)</t>
@@ -18996,7 +18996,7 @@
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>H | 358呎 (1房)
+          <t>H | 361呎 (1房)
 -
 -
 (待售)</t>
